--- a/ĐẦU VÀO/2026-06/GL_038_TK33895.xlsx
+++ b/ĐẦU VÀO/2026-06/GL_038_TK33895.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1. TCKT_PCVT\6. Thuế GTGT\THUE GTGT 2026\THUE GTGT 2026\T6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\DATA_THUE\THUE\ĐẦU VÀO\2026-06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC337BDE-2BF2-4BC9-91E8-83D906963990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9ACCC0E-2BA4-4F3E-A6E4-12D686C61C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{C3D755DE-75F0-4BB7-BC69-F501741BBF8A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{9062B060-B15E-4AC4-B0D6-B03B968A0CA3}"/>
   </bookViews>
   <sheets>
-    <sheet name="EVN_GL_038_–_sổ_chi_tiết_070726" sheetId="2" r:id="rId1"/>
+    <sheet name="EVN_GL_038_–_sổ_chi_tiết_110826" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="53">
   <si>
     <t>TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH</t>
   </si>
@@ -71,6 +71,167 @@
   </si>
   <si>
     <t>hệ GL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33895000000-Phải trả, phải nộp khác – Thuế đầu ra chưa kê khai </t>
+  </si>
+  <si>
+    <t>Số dư đầu kỳ</t>
+  </si>
+  <si>
+    <t>61 299 131 885</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Khác</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">          </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Khác</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Khác</t>
+    </r>
+  </si>
+  <si>
+    <t>GL-Manual</t>
+  </si>
+  <si>
+    <t>082900.000000.000.33895000000.0000.0000.000.000000.0000.0000</t>
+  </si>
+  <si>
+    <t>Giải trừ thuế GTGT đầu ra từ 33895 sang 333111 AR1647-31/05/2026</t>
+  </si>
+  <si>
+    <t>61 251 406 929</t>
+  </si>
+  <si>
+    <t>QUYENNN.HCM.VTA</t>
+  </si>
+  <si>
+    <t>Post</t>
+  </si>
+  <si>
+    <t>Giải trừ thuế GTGT đầu ra từ 33895 sang 333111 AR1649-31/05/2026</t>
+  </si>
+  <si>
+    <t>47 724 956</t>
+  </si>
+  <si>
+    <t>Giải trừ thuế GTGT đầu ra từ 33895 sang 333111 AR1648-31/05/2026</t>
+  </si>
+  <si>
+    <t>AR-Transaction</t>
+  </si>
+  <si>
+    <t>DIEN01-DOANH THU HÓA ĐƠN TIỀN ĐIỆN PHÁT SINH T06/2026</t>
+  </si>
+  <si>
+    <t>55 441 397 333</t>
+  </si>
+  <si>
+    <t>Final Post GL</t>
+  </si>
+  <si>
+    <t>DIEN00-DOANH THU HÓA ĐƠN TIỀN ĐIỆN PHÁT SINH-CT TNHH NHÔM TOÀN CẦU VIỆT NAM KỲ 3/6/2026</t>
+  </si>
+  <si>
+    <t>CSPK02-DOANH THU HÓA ĐƠN TIỀN VÔ CÔNG PHÁT SINH T06/2026</t>
+  </si>
+  <si>
+    <t>43 116 020</t>
+  </si>
+  <si>
+    <t>Cộng phát sinh – cấp 3</t>
+  </si>
+  <si>
+    <t>55 484 513 353</t>
+  </si>
+  <si>
+    <t>Dư cuối kỳ</t>
+  </si>
+  <si>
+    <t>Cộng phát sinh – cấp 2</t>
+  </si>
+  <si>
+    <r>
+      <t>Dư cuối kỳ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>Cộng phát sinh – cấp 1</t>
+  </si>
+  <si>
+    <r>
+      <t>Cộng phát sinh-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>33895000000</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Dư cuối kỳ-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
   </si>
   <si>
     <r>
@@ -107,23 +268,25 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
-    <font>
-      <sz val="12"/>
+  <fonts count="25" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Aptos Display"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
     </font>
@@ -131,99 +294,114 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Times New Roman"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Times New Roman"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Times New Roman"/>
+      <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Times New Roman"/>
+      <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Times New Roman"/>
+      <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C5700"/>
-      <name val="Times New Roman"/>
+      <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Times New Roman"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Times New Roman"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Times New Roman"/>
+      <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Times New Roman"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="0"/>
-      <name val="Times New Roman"/>
+      <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Times New Roman"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Times New Roman"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
-      <name val="Times New Roman"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -246,8 +424,21 @@
       <family val="1"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -733,66 +924,138 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="18" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="34" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -877,39 +1140,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -961,7 +1224,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1072,6 +1335,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -1080,13 +1350,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1151,294 +1414,768 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75AB9EC0-5565-473E-8E27-3703416C940C}">
-  <dimension ref="A1:I19"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61BD2585-8604-47AE-851C-A7763A00A9EE}">
+  <dimension ref="A1:I44"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.8984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-    </row>
-    <row r="3" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="24" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+    </row>
+    <row r="3" spans="1:9" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="25" t="s">
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="23"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-    </row>
-    <row r="7" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="47"/>
+    </row>
+    <row r="7" spans="1:9" ht="16.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="10" t="s">
+      <c r="C7" s="18"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="15" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11"/>
-      <c r="B8" s="10" t="s">
+    <row r="8" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="16"/>
+      <c r="B8" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
       <c r="H8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="11"/>
-    </row>
-    <row r="9" spans="1:9" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
+      <c r="I8" s="16"/>
+    </row>
+    <row r="9" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
       <c r="D9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="12"/>
-    </row>
-    <row r="10" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="16" t="s">
+      <c r="I9" s="17"/>
+    </row>
+    <row r="10" spans="1:9" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-    </row>
-    <row r="11" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="16" t="s">
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="23"/>
+    </row>
+    <row r="11" spans="1:9" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="24"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-    </row>
-    <row r="12" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
-      <c r="B12" s="16" t="s">
+      <c r="F11" s="8"/>
+      <c r="G11" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-    </row>
-    <row r="13" spans="1:9" ht="23.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="19"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="20" t="s">
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+    </row>
+    <row r="12" spans="1:9" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+    </row>
+    <row r="13" spans="1:9" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="19"/>
-    </row>
-    <row r="14" spans="1:9" ht="23.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="19"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="21" t="s">
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+    </row>
+    <row r="14" spans="1:9" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="19"/>
-    </row>
-    <row r="15" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="19"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="19"/>
-    </row>
-    <row r="16" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="19"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="19"/>
-    </row>
-    <row r="17" spans="1:5" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="19"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="19"/>
-    </row>
-    <row r="18" spans="1:5" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="19"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="19"/>
-    </row>
-    <row r="19" spans="1:5" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="19"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="19"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+    </row>
+    <row r="15" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="31">
+        <v>46184</v>
+      </c>
+      <c r="C15" s="29"/>
+      <c r="D15" s="33">
+        <v>1675</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="35"/>
+      <c r="H15" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="I15" s="33" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="30"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="34"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+    </row>
+    <row r="17" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="31">
+        <v>46184</v>
+      </c>
+      <c r="C17" s="29"/>
+      <c r="D17" s="33">
+        <v>1675</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" s="35"/>
+      <c r="H17" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="I17" s="33" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="30"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="34"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="34"/>
+    </row>
+    <row r="19" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="31">
+        <v>46184</v>
+      </c>
+      <c r="C19" s="29"/>
+      <c r="D19" s="33">
+        <v>1675</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="I19" s="33" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="30"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34"/>
+    </row>
+    <row r="21" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="31">
+        <v>46203</v>
+      </c>
+      <c r="C21" s="33">
+        <v>1782</v>
+      </c>
+      <c r="D21" s="29"/>
+      <c r="E21" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" s="35"/>
+      <c r="G21" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="H21" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="I21" s="33" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="30"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" s="36"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+    </row>
+    <row r="23" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="31">
+        <v>46203</v>
+      </c>
+      <c r="C23" s="33">
+        <v>1783</v>
+      </c>
+      <c r="D23" s="29"/>
+      <c r="E23" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="33" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="30"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="34"/>
+      <c r="I24" s="34"/>
+    </row>
+    <row r="25" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="31">
+        <v>46203</v>
+      </c>
+      <c r="C25" s="33">
+        <v>1784</v>
+      </c>
+      <c r="D25" s="29"/>
+      <c r="E25" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F25" s="35"/>
+      <c r="G25" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="H25" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="I25" s="33" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="30"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F26" s="36"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="34"/>
+      <c r="I26" s="34"/>
+    </row>
+    <row r="27" spans="1:9" ht="16.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="13"/>
+      <c r="B27" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H27" s="8"/>
+      <c r="I27" s="10"/>
+    </row>
+    <row r="28" spans="1:9" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="14"/>
+      <c r="B28" s="40" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="42"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+    </row>
+    <row r="29" spans="1:9" ht="16.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="14"/>
+      <c r="B29" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="42"/>
+      <c r="F29" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+    </row>
+    <row r="30" spans="1:9" ht="16.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="14"/>
+      <c r="B30" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="42"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
+    </row>
+    <row r="31" spans="1:9" ht="16.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="14"/>
+      <c r="B31" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="42"/>
+      <c r="F31" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+    </row>
+    <row r="32" spans="1:9" ht="16.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="14"/>
+      <c r="B32" s="40" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="41"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H32" s="10"/>
+      <c r="I32" s="10"/>
+    </row>
+    <row r="33" spans="1:9" ht="16.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="14"/>
+      <c r="B33" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="42"/>
+      <c r="F33" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+    </row>
+    <row r="34" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="14"/>
+      <c r="B34" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" s="41"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
+    </row>
+    <row r="35" spans="1:9" ht="16.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="14"/>
+      <c r="B35" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+    </row>
+    <row r="36" spans="1:9" ht="16.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="14"/>
+      <c r="B36" s="40" t="s">
+        <v>48</v>
+      </c>
+      <c r="C36" s="41"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
+    </row>
+    <row r="37" spans="1:9" ht="16.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="14"/>
+      <c r="B37" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37" s="41"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="42"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+    </row>
+    <row r="38" spans="1:9" ht="23.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="43"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="D38" s="44" t="s">
+        <v>51</v>
+      </c>
+      <c r="E38" s="43"/>
+    </row>
+    <row r="39" spans="1:9" ht="23.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="43"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="D39" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="E39" s="43"/>
+    </row>
+    <row r="40" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="43"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="43"/>
+    </row>
+    <row r="41" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="43"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="43"/>
+    </row>
+    <row r="42" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="43"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="43"/>
+    </row>
+    <row r="43" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="43"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="43"/>
+    </row>
+    <row r="44" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="43"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="43"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B12:E12"/>
+  <mergeCells count="78">
+    <mergeCell ref="B37:E37"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A6:I6"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="F15:F16"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="E7:E9"/>
